--- a/modules/apperp/management-aset/resources/laporan/laporan-penjualan-aset/standar.xlsx
+++ b/modules/apperp/management-aset/resources/laporan/laporan-penjualan-aset/standar.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="50">
   <si>
     <t>${kop.logo_kiri}</t>
   </si>
@@ -37,124 +37,136 @@
     <t>Laporan penjualan aset</t>
   </si>
   <si>
+    <t>Dari</t>
+  </si>
+  <si>
+    <t>${filter_dari}</t>
+  </si>
+  <si>
+    <t>Sampai</t>
+  </si>
+  <si>
+    <t>${filter_sampai}</t>
+  </si>
+  <si>
+    <t>Dicetak</t>
+  </si>
+  <si>
+    <t>${dicetak_pada}</t>
+  </si>
+  <si>
     <t>Group aset</t>
   </si>
   <si>
-    <t>${filter_group_aset}</t>
-  </si>
-  <si>
-    <t>Golongan aset</t>
-  </si>
-  <si>
-    <t>${filter_golongan_aset}</t>
+    <t>${filter_group}</t>
+  </si>
+  <si>
+    <t>Kelompok harta fiskal</t>
+  </si>
+  <si>
+    <t>${filter_golongan}</t>
   </si>
   <si>
     <t>Jenis aset</t>
   </si>
   <si>
-    <t>${filter_jenis_aset}</t>
+    <t>${filter_jenis}</t>
+  </si>
+  <si>
+    <t>Aset</t>
+  </si>
+  <si>
+    <t>${filter_aset}</t>
+  </si>
+  <si>
+    <t>Buku</t>
+  </si>
+  <si>
+    <t>${filter_buku}</t>
+  </si>
+  <si>
+    <t>Jumlah penjualan</t>
+  </si>
+  <si>
+    <t>${jumlah_penjualan}</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>${baris.nomor}</t>
+  </si>
+  <si>
+    <t>No. bukti</t>
+  </si>
+  <si>
+    <t>${baris.no_bukti}</t>
+  </si>
+  <si>
+    <t>Tanggal penjualan</t>
+  </si>
+  <si>
+    <t>${baris.tanggal_penjualan}</t>
+  </si>
+  <si>
+    <t>Kode aset</t>
+  </si>
+  <si>
+    <t>${baris.kode_aset}</t>
   </si>
   <si>
     <t>Nama aset</t>
   </si>
   <si>
-    <t>${filter_nama_aset}</t>
-  </si>
-  <si>
-    <t>Dari</t>
-  </si>
-  <si>
-    <t>${filter_dari}</t>
-  </si>
-  <si>
-    <t>Sampai</t>
-  </si>
-  <si>
-    <t>${filter_sampai}</t>
-  </si>
-  <si>
-    <t>Jumlah penjualan</t>
-  </si>
-  <si>
-    <t>${jumlah_penjualan}</t>
-  </si>
-  <si>
-    <t>Total nilai penjualan</t>
+    <t>${baris.nama_aset}</t>
+  </si>
+  <si>
+    <t>Spesifikasi</t>
+  </si>
+  <si>
+    <t>${baris.spesifikasi}</t>
+  </si>
+  <si>
+    <t>Buku penyusutan</t>
+  </si>
+  <si>
+    <t>${baris.buku}</t>
+  </si>
+  <si>
+    <t>Nilai penjualan</t>
+  </si>
+  <si>
+    <t>${baris.nilai_penjualan}</t>
+  </si>
+  <si>
+    <t>Nilai buku saat dijual</t>
+  </si>
+  <si>
+    <t>${baris.nilai_buku}</t>
+  </si>
+  <si>
+    <t>Laba / rugi</t>
+  </si>
+  <si>
+    <t>${baris.laba_rugi}</t>
+  </si>
+  <si>
+    <t>Keterangan</t>
+  </si>
+  <si>
+    <t>${baris.keterangan}</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
   <si>
     <t>${total_nilai_penjualan}</t>
   </si>
   <si>
-    <t>Dicetak</t>
-  </si>
-  <si>
-    <t>${dicetak_pada}</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>${baris.nomor}</t>
-  </si>
-  <si>
-    <t>No. Bukti</t>
-  </si>
-  <si>
-    <t>${baris.no_bukti}</t>
-  </si>
-  <si>
-    <t>Tgl Penjualan</t>
-  </si>
-  <si>
-    <t>${baris.tanggal_penjualan}</t>
-  </si>
-  <si>
-    <t>Kode Aset</t>
-  </si>
-  <si>
-    <t>${baris.asset_kode}</t>
-  </si>
-  <si>
-    <t>Item Aset</t>
-  </si>
-  <si>
-    <t>${baris.asset_nama}</t>
-  </si>
-  <si>
-    <t>Spesifikasi</t>
-  </si>
-  <si>
-    <t>${baris.spesifikasi}</t>
-  </si>
-  <si>
-    <t>Nilai Penjualan</t>
-  </si>
-  <si>
-    <t>${baris.nilai_penjualan}</t>
-  </si>
-  <si>
-    <t>Nilai Buku</t>
-  </si>
-  <si>
-    <t>${baris.nilai_buku}</t>
-  </si>
-  <si>
-    <t>Laba / Rugi</t>
-  </si>
-  <si>
-    <t>${baris.laba_rugi}</t>
-  </si>
-  <si>
-    <t>Keterangan</t>
-  </si>
-  <si>
-    <t>${baris.keterangan}</t>
-  </si>
-  <si>
-    <t>Status Dokumen</t>
-  </si>
-  <si>
-    <t>${baris.status_dokumen}</t>
+    <t>${total_nilai_buku}</t>
+  </si>
+  <si>
+    <t>${total_laba_rugi}</t>
   </si>
 </sst>
 </file>
@@ -200,7 +212,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -213,8 +225,14 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -240,11 +258,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
@@ -257,12 +286,13 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -561,22 +591,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
-    <col min="2" max="2" width="18" customWidth="true" style="0"/>
-    <col min="3" max="3" width="16" customWidth="true" style="0"/>
+    <col min="2" max="2" width="16" customWidth="true" style="0"/>
+    <col min="3" max="3" width="14" customWidth="true" style="0"/>
     <col min="4" max="4" width="16" customWidth="true" style="0"/>
-    <col min="5" max="5" width="22" customWidth="true" style="0"/>
-    <col min="6" max="6" width="22" customWidth="true" style="0"/>
-    <col min="7" max="7" width="20" customWidth="true" style="0"/>
+    <col min="5" max="5" width="30" customWidth="true" style="0"/>
+    <col min="6" max="6" width="28" customWidth="true" style="0"/>
+    <col min="7" max="7" width="18" customWidth="true" style="0"/>
     <col min="8" max="8" width="20" customWidth="true" style="0"/>
     <col min="9" max="9" width="20" customWidth="true" style="0"/>
-    <col min="10" max="10" width="28" customWidth="true" style="0"/>
-    <col min="11" max="11" width="16" customWidth="true" style="0"/>
+    <col min="10" max="10" width="20" customWidth="true" style="0"/>
+    <col min="11" max="11" width="36" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" customHeight="1" ht="22">
@@ -635,19 +664,19 @@
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C6" t="s">
         <v>8</v>
       </c>
+      <c r="D6" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" t="s">
         <v>10</v>
       </c>
-      <c r="H6" t="s">
+      <c r="F6" s="6" t="s">
         <v>11</v>
       </c>
     </row>
@@ -655,19 +684,19 @@
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C7" t="s">
         <v>14</v>
       </c>
+      <c r="D7" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="E7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" t="s">
         <v>16</v>
       </c>
-      <c r="H7" t="s">
+      <c r="F7" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -675,59 +704,59 @@
       <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D8" t="s">
+      <c r="C8" t="s">
         <v>20</v>
       </c>
+      <c r="D8" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" t="s">
         <v>22</v>
       </c>
-      <c r="H8" t="s">
+      <c r="F8" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:11" customHeight="1" ht="32">
+      <c r="A10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
@@ -745,13 +774,13 @@
       <c r="F11" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" t="s">
         <v>39</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" t="s">
         <v>41</v>
       </c>
       <c r="J11" t="s">
@@ -760,6 +789,27 @@
       <c r="K11" t="s">
         <v>45</v>
       </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A10:K10"/>
@@ -769,9 +819,10 @@
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="K1:K3"/>
+    <mergeCell ref="A12:G12"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
--- a/modules/apperp/management-aset/resources/laporan/laporan-penjualan-aset/standar.xlsx
+++ b/modules/apperp/management-aset/resources/laporan/laporan-penjualan-aset/standar.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="54">
   <si>
     <t>${kop.logo_kiri}</t>
   </si>
@@ -89,6 +89,18 @@
   </si>
   <si>
     <t>${jumlah_penjualan}</t>
+  </si>
+  <si>
+    <t>Lokasi</t>
+  </si>
+  <si>
+    <t>${filter_lokasi}</t>
+  </si>
+  <si>
+    <t>Kondisi</t>
+  </si>
+  <si>
+    <t>${filter_kondisi}</t>
   </si>
   <si>
     <t>No.</t>
@@ -720,79 +732,93 @@
         <v>23</v>
       </c>
     </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
     <row r="10" spans="1:11" customHeight="1" ht="32">
       <c r="A10" s="7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H11" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K11" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -801,13 +827,13 @@
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
       <c r="H12" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K12" s="8"/>
     </row>

--- a/modules/apperp/management-aset/resources/laporan/laporan-penjualan-aset/standar.xlsx
+++ b/modules/apperp/management-aset/resources/laporan/laporan-penjualan-aset/standar.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
   <si>
     <t>${kop.logo_kiri}</t>
   </si>
@@ -101,6 +101,12 @@
   </si>
   <si>
     <t>${filter_kondisi}</t>
+  </si>
+  <si>
+    <t>Filter tambahan</t>
+  </si>
+  <si>
+    <t>${filter_tambahan}</t>
   </si>
   <si>
     <t>No.</t>
@@ -745,80 +751,86 @@
       <c r="D9" s="6" t="s">
         <v>27</v>
       </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="10" spans="1:11" customHeight="1" ht="32">
       <c r="A10" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -827,13 +839,13 @@
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
       <c r="H12" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K12" s="8"/>
     </row>
